--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">

--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Failed: JDBC URL is required.</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed (100 samples)</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>

--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">

--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">

--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sai93\Documents\TestWeave\TestSuites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD245D66-C51B-477F-9A3F-A80FADE78B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC805747-294B-43C6-91E3-2F7932061031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCase1" sheetId="1" r:id="rId1"/>
+    <sheet name="TestCase2" sheetId="2" r:id="rId2"/>
+    <sheet name="TestCase3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="64">
   <si>
     <t>Test Suite</t>
   </si>
@@ -171,6 +173,57 @@
   </si>
   <si>
     <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"h2","value":"EventHub \u2014 Discover &amp; Book Events"},{"note":"Register","suggested":false,"action":"Click","selector":"a.text-indigo-600.hover\\:underline","value":""},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-email\"]","value":""},{"note":"","suggested":false,"action":"Type","selector":"[data-testid=\"register-email\"]","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[data-testid=\"register-password\"]","value":"Sai@ss15031993"},{"note":"","suggested":false,"action":"Click","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"Sai@ss15031993"},{"note":"Create Account","suggested":false,"action":"Click","selector":"[data-testid=\"register-btn\"]","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss15031993"},{"note":"Sign In","suggested":false,"action":"Click","selector":"#login-btn","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""}],"testName":"RegistrationFlow"}</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Execution Mode</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Sequential</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Failed: JDBC URL is required.</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>Passed (100 samples)</t>
+  </si>
+  <si>
+    <t>ParallelWebTest</t>
+  </si>
+  <si>
+    <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"/html/body/div[1]/div[2]/div[2]/div[1]/h2","value":"The #1 QA Practice Hub"},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai93@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""}],"testName":"Login Flow Test"}</t>
+  </si>
+  <si>
+    <t>ParallelWebTest2</t>
+  </si>
+  <si>
+    <t>{"headless":false,"startUrl":"https://demo.playwright.dev/todomvc","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"after #username","suggested":false,"action":"Navigate","selector":"","value":"https://rahulshettyacademy.com/loginpagePractise/"},{"note":"","suggested":false,"action":"Type","selector":"#username","value":"Sainath"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss150319993"},{"note":"","suggested":false,"action":"Validate Text","selector":"//*[@id=\"login-form\"]/div[4]/div/label[2]/span[1]","value":"User"},{"note":"User","suggested":false,"action":"Click","selector":"form#login-form &gt; div:nth-of-type(4) &gt; div &gt; label:nth-of-type(2)","value":""},{"note":"Okay","suggested":false,"action":"Click","selector":"#okayBtn","value":""}],"testName":"Login Flow Test"}</t>
+  </si>
+  <si>
+    <t>TestCase2</t>
+  </si>
+  <si>
+    <t>TestCase3</t>
   </si>
 </sst>
 </file>
@@ -512,8 +565,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="18.1796875" customWidth="1"/>
     <col min="3" max="3" width="24.08984375" customWidth="1"/>
@@ -904,7 +957,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1001,7 +1054,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1028,12 +1081,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GetBooks DB Validation</t>
+          <t>Registration Web Test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"authorization":{"type":"None","token":""},"headers":{"Accept":"application/json","User-Agent":"API-Validator-Tool/1.0","Content-Type":"application/json"},"endpoint":"http://216.10.245.166/Library/GetBook.php?AuthorName=Sainath","method":"GET","requestFormat":"JSON","headersText":"Accept: application/json\nContent-Type: application/json\nUser-Agent: API-Validator-Tool/1.0","params":{"AuthorName":"Sainath"},"authType":"None"}</t>
+          <t/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1043,7 +1096,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1063,7 +1116,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"stepType":"DB_VALIDATION","sqlQuery":"select * from books where author in (\"Sainath\")","dbColumnValidations":[{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"RestAssured SBA Assesment","actualValue":"RestAssured SBA Assesment","typeValidation":"string","dbColumnName":"book_name[0]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"ABCDEF","actualValue":"ABCDEF","typeValidation":"string","dbColumnName":"isbn[0]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"1236","actualValue":"1236","typeValidation":"string","dbColumnName":"aisle[0]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"Sainath","actualValue":"Sainath","typeValidation":"string","dbColumnName":"author[0]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"RestAssured SBA Assesment2","actualValue":"RestAssured SBA Assesment2","typeValidation":"string","dbColumnName":"book_name[1]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"SKLDJD","actualValue":"SKLDJD","typeValidation":"string","dbColumnName":"isbn[1]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"8911","actualValue":"8911","typeValidation":"string","dbColumnName":"aisle[1]","expectedValueOrVariable":""},{"result":"Not run","nullValidation":"Not Null","actualType":"string","previewValue":"Sainath","actualValue":"Sainath","typeValidation":"string","dbColumnName":"author[1]","expectedValueOrVariable":""}],"apiDbValidations":[{"description":"ISBN Should Match","apiField":"isbn","operator":"=","dbColumn":"isbn"},{"description":"Aisle Should Match","apiField":"aisle","operator":"=","dbColumn":"aisle"},{"description":"BookName Should Match","apiField":"book_name","operator":"=","dbColumn":"book_name"}],"databaseConnection":{"jdbcUrl":"jdbc:mysql://localhost:3306/apivalidator","databaseType":"MySQL","path":"C:\\Users\\sai93\\Documents\\api-validator\\DBConnection\\DBConnection\\db-connection.json","relativePath":"..\\..\\api-validator\\DBConnection\\DBConnection\\db-connection.json","driverClass":"com.mysql.cj.jdbc.Driver","username":"sainath"},"savedVariableSnapshot":{"root_0_.isbn":"ABCDEF","root_1_.book_name":"RestAssured SBA Assesment2","root_0_.book_name":"RestAssured SBA Assesment","root_0_.aisle":"1236","root_1_.aisle":"8911","root_1_.isbn":"SKLDJD"}}</t>
+          <t/>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1088,7 +1141,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t/>
+          <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"h2","value":"EventHub \u2014 Discover &amp; Book Events"},{"note":"Register","suggested":false,"action":"Click","selector":"a.text-indigo-600.hover\\:underline","value":""},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-email\"]","value":""},{"note":"","suggested":false,"action":"Type","selector":"[data-testid=\"register-email\"]","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[data-testid=\"register-password\"]","value":"Sai@ss15031993"},{"note":"","suggested":false,"action":"Click","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"Sai@ss15031993"},{"note":"Create Account","suggested":false,"action":"Click","selector":"[data-testid=\"register-btn\"]","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss15031993"},{"note":"Sign In","suggested":false,"action":"Click","selector":"#login-btn","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""}],"testName":"RegistrationFlow"}</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1108,7 +1161,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Failed: JDBC URL is required.</t>
+          <t>Failed (8 failed)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1178,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GetBooksNew DB Validation</t>
+          <t>TestCase1 Performance Test</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1140,7 +1193,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1165,22 +1218,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>{"jdbcUrl":"jdbc:mysql://localhost:3306/apivalidator","databaseType":"MySQL","path":"C:\\Users\\sai93\\Documents\\api-validator\\DBConnection\\DBConnection\\db-connection.json","relativePath":"..\\..\\api-validator\\DBConnection\\DBConnection\\db-connection.json","driverClass":"com.mysql.cj.jdbc.Driver","username":"sainath"}</t>
+          <t/>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>select * from books where author in ("Sainath")</t>
+          <t/>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[{"description":"ISBN Should Match","apiField":"isbn","operator":"=","dbColumn":"isbn"},{"description":"Aisle Should Match","apiField":"aisle","operator":"=","dbColumn":"aisle"},{"description":"BookName Should Match","apiField":"book_name","operator":"=","dbColumn":"book_name"}]</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"RestAssured SBA Assesment","actualValue":"RestAssured SBA Assesment","typeValidation":"string","dbColumnName":"book_name[0]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"ABCDEF","actualValue":"ABCDEF","typeValidation":"string","dbColumnName":"isbn[0]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"1236","actualValue":"1236","typeValidation":"string","dbColumnName":"aisle[0]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"Sainath","actualValue":"Sainath","typeValidation":"string","dbColumnName":"author[0]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"RestAssured SBA Assesment2","actualValue":"RestAssured SBA Assesment2","typeValidation":"string","dbColumnName":"book_name[1]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"SKLDJD","actualValue":"SKLDJD","typeValidation":"string","dbColumnName":"isbn[1]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"8911","actualValue":"8911","typeValidation":"string","dbColumnName":"aisle[1]","expectedValueOrVariable":""},{"result":"Passed","nullValidation":"Not Null","actualType":"string","previewValue":"Sainath","actualValue":"Sainath","typeValidation":"string","dbColumnName":"author[1]","expectedValueOrVariable":""}]</t>
+          <t/>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1190,12 +1243,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t/>
+          <t>{"stepType":"PERFORMANCE_TEST","iterationsPerThread":10,"threads":10,"requestBodySource":"Performance Test"}</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1205,396 +1258,382 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed (100 samples)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TestSuite1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TestCase1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Registration Web Test</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"h2","value":"EventHub \u2014 Discover &amp; Book Events"},{"note":"Register","suggested":false,"action":"Click","selector":"a.text-indigo-600.hover\\:underline","value":""},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-email\"]","value":""},{"note":"","suggested":false,"action":"Type","selector":"[data-testid=\"register-email\"]","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[data-testid=\"register-password\"]","value":"Sai@ss15031993"},{"note":"","suggested":false,"action":"Click","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"Sai@ss15031993"},{"note":"Create Account","suggested":false,"action":"Click","selector":"[data-testid=\"register-btn\"]","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss15031993"},{"note":"Sign In","suggested":false,"action":"Click","selector":"#login-btn","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""}],"testName":"RegistrationFlow"}</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Sequential</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D763EEA-D26E-4109-BDA2-92C939929960}">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TestSuite1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TestCase1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TestCase1 Performance Test</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{"authorization":{"type":"None","token":""},"headers":{"Accept":"application/json","User-Agent":"API-Validator-Tool/1.0","Content-Type":"application/json"},"endpoint":"http://216.10.245.166/Library/GetBook.php?AuthorName=Sainath","method":"GET","requestFormat":"JSON","headersText":"Accept: application/json\nContent-Type: application/json\nUser-Agent: API-Validator-Tool/1.0","params":{"AuthorName":"Sainath"},"authType":"None"}</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>{"stepType":"PERFORMANCE_TEST","iterationsPerThread":10,"threads":10,"requestBodySource":"Performance Test"}</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Sequential</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Passed (100 samples)</t>
-        </is>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TestSuite1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TestCase1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ParallelWebTest</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"/html/body/div[1]/div[2]/div[2]/div[1]/h2","value":"The #1 QA Practice Hub"},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai93@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""}],"testName":"Login Flow Test"}</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Sequential</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TestSuite1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TestCase1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ParallelWebTest2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{"headless":false,"startUrl":"https://demo.playwright.dev/todomvc","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"after #username","suggested":false,"action":"Navigate","selector":"","value":"https://rahulshettyacademy.com/loginpagePractise/"},{"note":"","suggested":false,"action":"Type","selector":"#username","value":"Sainath"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss150319993"},{"note":"","suggested":false,"action":"Validate Text","selector":"//*[@id=\"login-form\"]/div[4]/div/label[2]/span[1]","value":"User"},{"note":"User","suggested":false,"action":"Click","selector":"form#login-form &gt; div:nth-of-type(4) &gt; div &gt; label:nth-of-type(2)","value":""},{"note":"Okay","suggested":false,"action":"Click","selector":"#okayBtn","value":""}],"testName":"Login Flow Test"}</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Sequential</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691F5CB7-1B25-45F5-AF32-A5AE5BE57481}">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/testweave/test-suite.xlsx
+++ b/testweave/test-suite.xlsx
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Registration Web Test</t>
+          <t>TestCase1 Performance Test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>{"authorization":{"type":"None","token":""},"headers":{"Accept":"application/json","User-Agent":"API-Validator-Tool/1.0","Content-Type":"application/json"},"endpoint":"http://216.10.245.166/Library/GetBook.php?AuthorName=Sainath","method":"GET","requestFormat":"JSON","headersText":"Accept: application/json\nContent-Type: application/json\nUser-Agent: API-Validator-Tool/1.0","params":{"AuthorName":"Sainath"},"authType":"None"}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>{"headless":false,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","suggested":false,"action":"Navigate","selector":"","value":"https://eventhub.rahulshettyacademy.com/login"},{"note":"Suggested after navigation","suggested":true,"action":"Validate Text","selector":"h2","value":"EventHub \u2014 Discover &amp; Book Events"},{"note":"Register","suggested":false,"action":"Click","selector":"a.text-indigo-600.hover\\:underline","value":""},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-email\"]","value":""},{"note":"","suggested":false,"action":"Type","selector":"[data-testid=\"register-email\"]","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"[data-testid=\"register-password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[data-testid=\"register-password\"]","value":"Sai@ss15031993"},{"note":"","suggested":false,"action":"Click","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"Sai@ss15031993"},{"note":"Create Account","suggested":false,"action":"Click","selector":"[data-testid=\"register-btn\"]","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""},{"note":"","suggested":false,"action":"Click","selector":"#email","value":""},{"note":"","suggested":false,"action":"Type","selector":"#email","value":"sai5611@live.in"},{"note":"","suggested":false,"action":"Click","selector":"#password","value":""},{"note":"password input","suggested":false,"action":"Type","selector":"#password","value":"Sai@ss15031993"},{"note":"Sign In","suggested":false,"action":"Click","selector":"#login-btn","value":""},{"note":"Logout","suggested":false,"action":"Click","selector":"[data-testid=\"logout-btn\"]","value":""}],"testName":"RegistrationFlow"}</t>
+          <t/>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t/>
+          <t>{"stepType":"PERFORMANCE_TEST","iterationsPerThread":10,"threads":10,"requestBodySource":"Performance Test"}</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Failed (8 failed)</t>
+          <t>Passed (100 samples)</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TestCase1 Performance Test</t>
+          <t>WebUI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{"authorization":{"type":"None","token":""},"headers":{"Accept":"application/json","User-Agent":"API-Validator-Tool/1.0","Content-Type":"application/json"},"endpoint":"http://216.10.245.166/Library/GetBook.php?AuthorName=Sainath","method":"GET","requestFormat":"JSON","headersText":"Accept: application/json\nContent-Type: application/json\nUser-Agent: API-Validator-Tool/1.0","params":{"AuthorName":"Sainath"},"authType":"None"}</t>
+          <t/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t/>
+          <t>{"headless":true,"startUrl":"https://eventhub.rahulshettyacademy.com/login","stepType":"WEB_TEST","slowMoMillis":0,"steps":[{"note":"page loaded","flowVariableName":"","stepName":"Navigate page loaded","action":"Navigate","step":"1","selector":"","value":"https://eventhub.rahulshettyacademy.com/login","timeout":""},{"note":"Correct Flow Variable syntax while preserving unique reusable email","flowVariableName":"email","stepName":"Flow Variable email","action":"Flow Variable","step":"2","selector":"email","value":"sai${randomInt}@live.in","timeout":""},{"note":"Healed Get Text selector to uniquely target the visible EventHub heading","flowVariableName":"","stepName":"Get Text EventHub Practice App","action":"Get Text","step":"3","selector":"text=\"EventHub \u2014 Practice App\"","value":"EventHub \u2014 Practice App","timeout":""},{"note":"Register","flowVariableName":"","stepName":"Click a text-indigo-600 hover underline","action":"Click","step":"4","selector":"a.text-indigo-600.hover\\:underline","value":"","timeout":""},{"note":"","flowVariableName":"","stepName":"Click register-email","action":"Click","step":"5","selector":"[data-testid=\"register-email\"]","value":"","timeout":""},{"note":"","flowVariableName":"","stepName":"Type register-email","action":"Type","step":"6","selector":"[data-testid=\"register-email\"]","value":"${email}","timeout":""},{"note":"","flowVariableName":"","stepName":"Click register-password","action":"Click","step":"7","selector":"[data-testid=\"register-password\"]","value":"","timeout":""},{"note":"password input","flowVariableName":"","stepName":"Type register-password","action":"Type","step":"8","selector":"[data-testid=\"register-password\"]","value":"Sai@ss15031993","timeout":""},{"note":"","flowVariableName":"","stepName":"Click Repeat your password","action":"Click","step":"9","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"","timeout":""},{"note":"password input","flowVariableName":"","stepName":"Type Repeat your password","action":"Type","step":"10","selector":"[placeholder=\"Repeat\\ your\\ password\"]","value":"Sai@ss15031993","timeout":""},{"note":"Create Account","flowVariableName":"","stepName":"Click register-btn","action":"Click","step":"11","selector":"[data-testid=\"register-btn\"]","value":"","timeout":""},{"note":"Logout","flowVariableName":"","stepName":"Click logout-btn","action":"Click","step":"12","selector":"[data-testid=\"logout-btn\"]","value":"","timeout":""},{"note":"","flowVariableName":"","stepName":"Click email","action":"Click","step":"13","selector":"#email","value":"","timeout":""},{"note":"","flowVariableName":"","stepName":"Type email","action":"Type","step":"14","selector":"#email","value":"${email}","timeout":""},{"note":"","flowVariableName":"","stepName":"Click password","action":"Click","step":"15","selector":"#password","value":"","timeout":""},{"note":"password input","flowVariableName":"","stepName":"Type password","action":"Type","step":"16","selector":"#password","value":"Sai@ss15031993","timeout":""},{"note":"Sign In","flowVariableName":"","stepName":"Click login-btn","action":"Click","step":"17","selector":"#login-btn","value":"","timeout":""},{"note":"Logout","flowVariableName":"","stepName":"Click logout-btn","action":"Click","step":"18","selector":"[data-testid=\"logout-btn\"]","value":"","timeout":""}],"testName":"RegistrationFlow"}</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>{"stepType":"PERFORMANCE_TEST","iterationsPerThread":10,"threads":10,"requestBodySource":"Performance Test"}</t>
+          <t/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Passed (100 samples)</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
